--- a/AHR_data 29th.xlsx
+++ b/AHR_data 29th.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tn/Desktop/REASON/AHR_50states/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA3AA70-7E96-2845-917D-3E4343212EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683E00E2-0DCD-8B4B-B885-AFECDB1BFFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="12120" windowWidth="28320" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6080" yWindow="500" windowWidth="42980" windowHeight="21500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHR Data" sheetId="1" r:id="rId1"/>
@@ -802,6 +802,7 @@
   <dimension ref="A1:AO52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="37" max="37" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
@@ -11849,9 +11850,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E579C8-CF2F-714C-9021-8ABE1BE9EDFF}">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="17" max="17" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
@@ -14231,7 +14233,7 @@
         <v>10</v>
       </c>
       <c r="Q45" s="3">
-        <v>35.185021410804893</v>
+        <v>16.20624617038051</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
@@ -14284,7 +14286,7 @@
         <v>38</v>
       </c>
       <c r="Q46" s="3">
-        <v>16.20624617038051</v>
+        <v>12.520138123251989</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
@@ -14337,7 +14339,7 @@
         <v>1</v>
       </c>
       <c r="Q47" s="3">
-        <v>12.520138123251989</v>
+        <v>32.816663209899183</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
@@ -14390,7 +14392,7 @@
         <v>48</v>
       </c>
       <c r="Q48" s="3">
-        <v>32.816663209899183</v>
+        <v>33.78096984562103</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
@@ -14443,7 +14445,7 @@
         <v>30</v>
       </c>
       <c r="Q49" s="3">
-        <v>33.78096984562103</v>
+        <v>12.46680577663755</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
@@ -14496,7 +14498,7 @@
         <v>31</v>
       </c>
       <c r="Q50" s="3">
-        <v>12.46680577663755</v>
+        <v>16.905125974804651</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
@@ -14549,11 +14551,6 @@
         <v>20</v>
       </c>
       <c r="Q51" s="3">
-        <v>16.905125974804651</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="Q52" s="3">
         <v>11.588262632083939</v>
       </c>
     </row>
